--- a/test_export.xlsx
+++ b/test_export.xlsx
@@ -37,7 +37,7 @@
     <t>06 ABC 123</t>
   </si>
   <si>
-    <t>YAKIT_LISTESI RAPORU - 02.03.2026 20:22</t>
+    <t>YAKIT_LISTESI RAPORU - 16.03.2026 20:13</t>
   </si>
 </sst>
 </file>
